--- a/note/專案管理.xlsx
+++ b/note/專案管理.xlsx
@@ -1,37 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aidara\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1706D347-76FA-404E-820C-0B1BC5E08D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E046B63-1F95-4AB5-81A7-0726587BD86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="優照護模式比較" sheetId="2" r:id="rId1"/>
     <sheet name="優照護系統比較" sheetId="3" r:id="rId2"/>
     <sheet name="WBS" sheetId="4" r:id="rId3"/>
     <sheet name="初階甘特圖" sheetId="5" r:id="rId4"/>
+    <sheet name="初階甘特圖 (2)" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">WBS!$A$1:$G$28</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="149">
   <si>
     <t>雇主</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -653,6 +665,10 @@
   </si>
   <si>
     <t>歷史紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>註冊/商店資訊模組v2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -830,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -849,9 +865,6 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -861,17 +874,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -880,14 +883,12 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -903,6 +904,22 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1590,15 +1607,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>451057</xdr:colOff>
+      <xdr:colOff>451056</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>154240</xdr:rowOff>
+      <xdr:rowOff>154239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>11430</xdr:colOff>
+      <xdr:colOff>158749</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>286338</xdr:rowOff>
+      <xdr:rowOff>279400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1621,8 +1638,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4672537" y="2825050"/>
-          <a:ext cx="169973" cy="132098"/>
+          <a:off x="4673806" y="2827589"/>
+          <a:ext cx="317293" cy="125161"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1634,15 +1651,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>148231</xdr:colOff>
+      <xdr:colOff>120216</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>100198</xdr:rowOff>
+      <xdr:rowOff>49772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>590852</xdr:colOff>
+      <xdr:colOff>562837</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>231793</xdr:rowOff>
+      <xdr:rowOff>181367</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1665,7 +1682,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4995398" y="3127031"/>
+          <a:off x="4949391" y="3040622"/>
           <a:ext cx="442621" cy="131595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1680,13 +1697,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>547980</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>107834</xdr:rowOff>
+      <xdr:rowOff>70562</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>270698</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>239429</xdr:rowOff>
+      <xdr:rowOff>202157</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1709,8 +1726,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5385319" y="3441584"/>
-          <a:ext cx="335040" cy="131595"/>
+          <a:off x="5372600" y="3375323"/>
+          <a:ext cx="331489" cy="131595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2203,6 +2220,1463 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>130940</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>180013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>554933</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>306295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="圖片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C05FBB09-2E03-429A-BD34-62D463AA8BCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4955560" y="3161752"/>
+          <a:ext cx="423993" cy="126282"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>556666</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>199891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>260902</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="圖片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08777E0D-38A1-4230-9866-63D59D17E9FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5381286" y="3504652"/>
+          <a:ext cx="313007" cy="123131"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>290879</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>46160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>332154</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>177755</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4A3290E-37E2-46E3-949E-7BC9BFC815B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2386379" y="446210"/>
+          <a:ext cx="336550" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>791310</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>169985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>327757</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>302083</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="圖片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC5192AF-9A50-429A-8F5E-A8890C53213C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2391510" y="570035"/>
+          <a:ext cx="327022" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>278179</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>60813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1955</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>192408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="圖片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4034F7B3-0F7E-4F31-B5BE-1137AF0D9FDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2668954" y="784713"/>
+          <a:ext cx="333376" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>283310</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>184638</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>5495</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>316736</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="圖片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C67BBEE-4E48-4B86-93C9-4942607BD058}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2674085" y="908538"/>
+          <a:ext cx="331785" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>603617</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>37001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>433917</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>168596</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="圖片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46806C6F-6A2F-403A-8918-154DB383B0F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2994392" y="1084751"/>
+          <a:ext cx="439900" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>206</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>160826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>292924</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="圖片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E0B48FA-F43D-4F9E-BA8D-7555FDDF115D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3000581" y="1208576"/>
+          <a:ext cx="428419" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>406766</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>35942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>237066</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>167537</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="圖片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97212F98-376D-468B-83C3-DCB3A4B5C090}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3407141" y="1407542"/>
+          <a:ext cx="439900" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>411897</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>159767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>231774</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>291865</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="圖片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CD2DC22-F2F8-4B5B-947B-067CA64DEEC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3412272" y="1531367"/>
+          <a:ext cx="429477" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>227909</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>31710</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>560227</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>163305</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="圖片 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0180A1E-0B71-443D-A96D-57AF58BBE4B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3837884" y="1727160"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>233040</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>155535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>563767</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>287633</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="圖片 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5DB9DC5-3D72-44B6-AC48-110C0775A2BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3843015" y="1850985"/>
+          <a:ext cx="330727" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>550701</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>34356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>273419</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>165951</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="圖片 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7356A3B-8373-4E98-97CE-240470EFEDF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4160676" y="2053656"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>555832</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>158181</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>276959</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>290279</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="圖片 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63AD6F78-5F07-42A9-A0D3-4D6435E35252}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4165807" y="2177481"/>
+          <a:ext cx="330727" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>262230</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>39799</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>448822</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>171394</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="圖片 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A829311C-6F6A-4B96-9C84-49484A361169}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4481805" y="2382949"/>
+          <a:ext cx="186592" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>267361</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>163624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>446328</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>295722</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="圖片 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA5A0AC3-1B07-4E8F-A1A0-4D8D7A7FCFC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4486936" y="2506774"/>
+          <a:ext cx="178967" cy="132098"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>445926</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>30415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>168644</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>162010</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="圖片 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4792CC42-1A7F-4016-ABC5-71DEDBE6A303}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4665501" y="2697415"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>451056</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>154239</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>158749</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="圖片 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7959B1C1-834F-4CBA-85D0-E72294EFB979}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4670631" y="2821239"/>
+          <a:ext cx="317293" cy="125161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>120216</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>49772</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>562837</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>181367</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="圖片 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A57EA31D-4120-4867-9117-064A1B74EBD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4949391" y="3040622"/>
+          <a:ext cx="442621" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>547980</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>70562</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>270698</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>202157</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="圖片 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D04F706-8FD4-47B8-8172-90E36AD30A7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5377155" y="3385262"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>288270</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>94697</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>285749</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>226292</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="圖片 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73809CB9-264E-4A38-A242-430051A2ABF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5727045" y="3733247"/>
+          <a:ext cx="607079" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>335140</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>87894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>57857</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>219489</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="圖片 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AC35964-45AA-4AB8-9574-2B04DF24D7BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6993115" y="4697994"/>
+          <a:ext cx="332317" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>57970</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>110177</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>500591</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>241772</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="圖片 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FAEF92-8B39-4555-93D6-47C272B8A4C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7325545" y="5044127"/>
+          <a:ext cx="442621" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>511882</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>91068</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>234600</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>222663</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="圖片 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BC14853-09D8-4A0E-8F3D-3702FA1B4A15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7779457" y="5348868"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>267559</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>107247</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>307975</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>238842</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="圖片 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADFD3993-7B48-4544-8141-CC805E0939D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8144734" y="5688897"/>
+          <a:ext cx="650016" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>286609</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>94547</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>327025</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>226142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="圖片 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E6FD9EF-0886-470D-A42C-23924C91C237}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8773384" y="6000047"/>
+          <a:ext cx="650016" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>346782</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>110118</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>69500</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>241713</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="圖片 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CB17C5A-5A4F-4071-8B33-C13F45F1DD9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9443157" y="6339468"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>99132</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>116468</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>431450</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>248063</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="圖片 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAF1EA72-B08B-4D2B-A9C0-9EEB1B4CDEA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9805107" y="6669668"/>
+          <a:ext cx="332318" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>450270</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>103997</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>27262</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>235592</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="圖片 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBC9A11D-F011-4363-8920-C6CEBDEF0A12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10156245" y="6981047"/>
+          <a:ext cx="186592" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>130940</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>180013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>554933</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>306295</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="圖片 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FA2106D-6D53-4652-BC87-1AB59D9760D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4960115" y="3170863"/>
+          <a:ext cx="423993" cy="126282"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>556666</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>199891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>260902</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="圖片 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4EE753E-8491-408C-BD23-7DF0B4F0087A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5385841" y="3514591"/>
+          <a:ext cx="313836" cy="123959"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>137821</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>214145</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="圖片 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97947E6-B0BF-4B43-896B-AA4D61C6BB68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6356350" y="4051300"/>
+          <a:ext cx="442621" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>588671</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>226845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="圖片 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADF8913-2A6D-4056-BCA5-6E424A7066DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6807200" y="4387850"/>
+          <a:ext cx="442621" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2473,9 +3947,9 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
-    <col min="2" max="2" width="14.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="39.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="39.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="44.7109375" style="4" customWidth="1"/>
     <col min="5" max="5" width="4.5703125" style="4" customWidth="1"/>
     <col min="6" max="6" width="51.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.140625" style="4" bestFit="1" customWidth="1"/>
@@ -2543,7 +4017,7 @@
       <c r="F5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2560,7 +4034,7 @@
       <c r="F6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2568,14 +4042,14 @@
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="29"/>
+      <c r="F7" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="14"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
@@ -2590,7 +4064,7 @@
       <c r="F8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2598,10 +4072,10 @@
       <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="29"/>
       <c r="F9" s="5" t="s">
         <v>31</v>
       </c>
@@ -2619,10 +4093,10 @@
       <c r="D10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2636,10 +4110,10 @@
       <c r="D11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="18"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
@@ -2659,52 +4133,52 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2779,8 +4253,8 @@
       <c r="B7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2797,8 +4271,8 @@
       <c r="B9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
@@ -2861,7 +4335,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="18" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2872,7 +4346,7 @@
       <c r="B3">
         <v>10</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>58</v>
       </c>
       <c r="D3" t="s">
@@ -2885,7 +4359,7 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <f>E3+F3</f>
+        <f t="shared" ref="G3:G9" si="0">E3+F3</f>
         <v>8</v>
       </c>
     </row>
@@ -2896,7 +4370,7 @@
       <c r="B4">
         <v>180</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="14" t="s">
         <v>57</v>
       </c>
       <c r="D4" t="s">
@@ -2909,7 +4383,7 @@
         <v>4</v>
       </c>
       <c r="G4">
-        <f>E4+F4</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -2920,7 +4394,7 @@
       <c r="B5">
         <v>120</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>99</v>
       </c>
       <c r="D5" t="s">
@@ -2933,7 +4407,7 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <f>E5+F5</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -2944,7 +4418,7 @@
       <c r="B6">
         <v>140</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>75</v>
       </c>
       <c r="D6" t="s">
@@ -2957,7 +4431,7 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <f>E6+F6</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -2968,7 +4442,7 @@
       <c r="B7">
         <v>130</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D7" t="s">
@@ -2981,7 +4455,7 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <f>E7+F7</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -2992,7 +4466,7 @@
       <c r="B8">
         <v>150</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="14" t="s">
         <v>79</v>
       </c>
       <c r="D8" t="s">
@@ -3005,7 +4479,7 @@
         <v>8</v>
       </c>
       <c r="G8">
-        <f>E8+F8</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -3016,7 +4490,7 @@
       <c r="B9">
         <v>80</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>93</v>
       </c>
       <c r="D9" t="s">
@@ -3029,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <f>E9+F9</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -3037,7 +4511,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="19" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3048,7 +4522,7 @@
       <c r="B11">
         <v>30</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="15" t="s">
         <v>62</v>
       </c>
       <c r="D11" t="s">
@@ -3072,7 +4546,7 @@
       <c r="B12">
         <v>40</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="15" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
@@ -3096,7 +4570,7 @@
       <c r="B13">
         <v>50</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="15" t="s">
         <v>84</v>
       </c>
       <c r="D13" t="s">
@@ -3120,7 +4594,7 @@
       <c r="B14">
         <v>160</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="15" t="s">
         <v>89</v>
       </c>
       <c r="D14" t="s">
@@ -3144,7 +4618,7 @@
       <c r="B15">
         <v>100</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="15" t="s">
         <v>91</v>
       </c>
       <c r="D15" t="s">
@@ -3165,7 +4639,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="20" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3176,7 +4650,7 @@
       <c r="B17">
         <v>60</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="16" t="s">
         <v>62</v>
       </c>
       <c r="D17" t="s">
@@ -3200,7 +4674,7 @@
       <c r="B18">
         <v>70</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="16" t="s">
         <v>86</v>
       </c>
       <c r="D18" t="s">
@@ -3224,7 +4698,7 @@
       <c r="B19">
         <v>90</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="16" t="s">
         <v>83</v>
       </c>
       <c r="D19" t="s">
@@ -3248,7 +4722,7 @@
       <c r="B20">
         <v>110</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="16" t="s">
         <v>95</v>
       </c>
       <c r="D20" t="s">
@@ -3269,7 +4743,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="21" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3280,7 +4754,7 @@
       <c r="B22">
         <v>160</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="17" t="s">
         <v>94</v>
       </c>
       <c r="D22" t="s">
@@ -3304,7 +4778,7 @@
       <c r="B23">
         <v>105</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="17" t="s">
         <v>97</v>
       </c>
       <c r="D23" t="s">
@@ -3328,7 +4802,7 @@
       <c r="B24">
         <v>170</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="17" t="s">
         <v>60</v>
       </c>
       <c r="D24" t="s">
@@ -3352,7 +4826,7 @@
       <c r="B25">
         <v>65</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="17" t="s">
         <v>63</v>
       </c>
       <c r="D25" t="s">
@@ -3373,13 +4847,12 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="C26" s="27"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" t="s">
         <v>110</v>
       </c>
       <c r="E27">
@@ -3399,7 +4872,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" t="s">
         <v>111</v>
       </c>
       <c r="E28">
@@ -3433,7 +4906,6 @@
   <cols>
     <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.25">
@@ -3448,8 +4920,8 @@
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="28"/>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
         <v>117</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -3493,10 +4965,10 @@
       </c>
     </row>
     <row r="3" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="23">
         <v>4</v>
       </c>
       <c r="D3" s="3"/>
@@ -3505,7 +4977,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="30"/>
+      <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -3514,10 +4986,10 @@
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="23">
         <v>4</v>
       </c>
       <c r="D4" s="3"/>
@@ -3526,7 +4998,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="30"/>
+      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -3535,10 +5007,10 @@
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="23">
         <v>2</v>
       </c>
       <c r="D5" s="3"/>
@@ -3547,7 +5019,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="30"/>
+      <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -3556,10 +5028,10 @@
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="23">
         <v>2</v>
       </c>
       <c r="D6" s="3"/>
@@ -3568,7 +5040,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="30"/>
+      <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -3577,17 +5049,17 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="30"/>
+      <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -3596,17 +5068,17 @@
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="30"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3615,17 +5087,17 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="30"/>
+      <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -3634,10 +5106,10 @@
       <c r="P9" s="3"/>
     </row>
     <row r="10" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="23">
         <v>8</v>
       </c>
       <c r="D10" s="3"/>
@@ -3646,7 +5118,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="30"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -3655,10 +5127,10 @@
       <c r="P10" s="3"/>
     </row>
     <row r="11" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="23">
         <v>2</v>
       </c>
       <c r="D11" s="3"/>
@@ -3667,7 +5139,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="30"/>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -3676,10 +5148,10 @@
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="23">
         <v>2</v>
       </c>
       <c r="D12" s="3"/>
@@ -3688,7 +5160,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="30"/>
+      <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -3697,10 +5169,10 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="23">
         <v>2</v>
       </c>
       <c r="D13" s="3"/>
@@ -3709,7 +5181,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="30"/>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -3718,10 +5190,10 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="23">
         <v>2</v>
       </c>
       <c r="D14" s="3"/>
@@ -3730,7 +5202,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="30"/>
+      <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -3739,10 +5211,10 @@
       <c r="P14" s="3"/>
     </row>
     <row r="15" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="23">
         <v>6</v>
       </c>
       <c r="D15" s="3"/>
@@ -3751,7 +5223,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="30"/>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -3760,10 +5232,10 @@
       <c r="P15" s="3"/>
     </row>
     <row r="16" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="23">
         <v>1</v>
       </c>
       <c r="D16" s="3"/>
@@ -3772,7 +5244,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="30"/>
+      <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -3781,10 +5253,10 @@
       <c r="P16" s="3"/>
     </row>
     <row r="17" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="23">
         <v>1</v>
       </c>
       <c r="D17" s="3"/>
@@ -3793,7 +5265,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="30"/>
+      <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -3802,10 +5274,10 @@
       <c r="P17" s="3"/>
     </row>
     <row r="18" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="23">
         <v>2</v>
       </c>
       <c r="D18" s="3"/>
@@ -3814,7 +5286,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="30"/>
+      <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -3823,10 +5295,10 @@
       <c r="P18" s="3"/>
     </row>
     <row r="19" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="23">
         <v>2</v>
       </c>
       <c r="D19" s="3"/>
@@ -3835,7 +5307,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="30"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -3844,10 +5316,10 @@
       <c r="P19" s="3"/>
     </row>
     <row r="20" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="23">
         <v>4</v>
       </c>
       <c r="D20" s="3"/>
@@ -3856,7 +5328,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="30"/>
+      <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -3865,10 +5337,10 @@
       <c r="P20" s="3"/>
     </row>
     <row r="21" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="23">
         <v>2</v>
       </c>
       <c r="D21" s="3"/>
@@ -3877,7 +5349,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="30"/>
+      <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -3886,10 +5358,10 @@
       <c r="P21" s="3"/>
     </row>
     <row r="22" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="23">
         <v>2</v>
       </c>
       <c r="D22" s="3"/>
@@ -3898,7 +5370,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="30"/>
+      <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -3907,10 +5379,10 @@
       <c r="P22" s="3"/>
     </row>
     <row r="23" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="23">
         <v>4</v>
       </c>
       <c r="D23" s="3"/>
@@ -3919,7 +5391,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="30"/>
+      <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -3928,10 +5400,10 @@
       <c r="P23" s="3"/>
     </row>
     <row r="24" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="23">
         <v>2</v>
       </c>
       <c r="D24" s="3"/>
@@ -3940,7 +5412,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="30"/>
+      <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -3949,10 +5421,10 @@
       <c r="P24" s="3"/>
     </row>
     <row r="25" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="23">
         <v>2</v>
       </c>
       <c r="D25" s="3"/>
@@ -3961,7 +5433,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="30"/>
+      <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -3970,10 +5442,10 @@
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="23">
         <v>2</v>
       </c>
       <c r="D26" s="3"/>
@@ -3982,7 +5454,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="30"/>
+      <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -3991,10 +5463,10 @@
       <c r="P26" s="3"/>
     </row>
     <row r="27" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="23">
         <v>1</v>
       </c>
       <c r="D27" s="3"/>
@@ -4003,7 +5475,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="30"/>
+      <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -4012,10 +5484,10 @@
       <c r="P27" s="3"/>
     </row>
     <row r="28" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="23">
         <v>1</v>
       </c>
       <c r="D28" s="3"/>
@@ -4024,7 +5496,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="30"/>
+      <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -4033,10 +5505,10 @@
       <c r="P28" s="3"/>
     </row>
     <row r="29" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="23">
         <v>4</v>
       </c>
       <c r="D29" s="3"/>
@@ -4045,7 +5517,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="30"/>
+      <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -4054,10 +5526,10 @@
       <c r="P29" s="3"/>
     </row>
     <row r="30" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="23">
         <v>2</v>
       </c>
       <c r="D30" s="3"/>
@@ -4066,7 +5538,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="30"/>
+      <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -4075,10 +5547,10 @@
       <c r="P30" s="3"/>
     </row>
     <row r="31" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="23">
         <v>2</v>
       </c>
       <c r="D31" s="3"/>
@@ -4087,7 +5559,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="30"/>
+      <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -4096,17 +5568,17 @@
       <c r="P31" s="3"/>
     </row>
     <row r="32" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="29"/>
+      <c r="C32" s="23"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="30"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -4115,17 +5587,17 @@
       <c r="P32" s="3"/>
     </row>
     <row r="33" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="29"/>
+      <c r="C33" s="23"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="30"/>
+      <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -4134,10 +5606,10 @@
       <c r="P33" s="3"/>
     </row>
     <row r="34" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="23">
         <v>6</v>
       </c>
       <c r="D34" s="3"/>
@@ -4146,7 +5618,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="30"/>
+      <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -4155,10 +5627,10 @@
       <c r="P34" s="3"/>
     </row>
     <row r="35" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="23">
         <v>2</v>
       </c>
       <c r="D35" s="3"/>
@@ -4167,7 +5639,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="30"/>
+      <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -4176,10 +5648,10 @@
       <c r="P35" s="3"/>
     </row>
     <row r="36" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="23">
         <v>2</v>
       </c>
       <c r="D36" s="3"/>
@@ -4188,7 +5660,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="30"/>
+      <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -4197,10 +5669,10 @@
       <c r="P36" s="3"/>
     </row>
     <row r="37" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="23">
         <v>2</v>
       </c>
       <c r="D37" s="3"/>
@@ -4209,7 +5681,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="30"/>
+      <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -4218,10 +5690,10 @@
       <c r="P37" s="3"/>
     </row>
     <row r="38" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="23">
         <v>4</v>
       </c>
       <c r="D38" s="3"/>
@@ -4230,7 +5702,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="30"/>
+      <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -4239,17 +5711,17 @@
       <c r="P38" s="3"/>
     </row>
     <row r="39" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="29"/>
+      <c r="C39" s="23"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="30"/>
+      <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -4258,17 +5730,17 @@
       <c r="P39" s="3"/>
     </row>
     <row r="40" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="29"/>
+      <c r="C40" s="23"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="30"/>
+      <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
@@ -4277,17 +5749,17 @@
       <c r="P40" s="3"/>
     </row>
     <row r="41" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C41" s="29"/>
+      <c r="C41" s="23"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="30"/>
+      <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4296,17 +5768,17 @@
       <c r="P41" s="3"/>
     </row>
     <row r="42" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="C42" s="29"/>
+      <c r="C42" s="23"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="30"/>
+      <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -4315,10 +5787,10 @@
       <c r="P42" s="3"/>
     </row>
     <row r="43" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="23">
         <v>4</v>
       </c>
       <c r="D43" s="3"/>
@@ -4327,7 +5799,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="30"/>
+      <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
@@ -4336,10 +5808,10 @@
       <c r="P43" s="3"/>
     </row>
     <row r="44" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="23">
         <v>4</v>
       </c>
       <c r="D44" s="3"/>
@@ -4348,7 +5820,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="30"/>
+      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4357,10 +5829,10 @@
       <c r="P44" s="3"/>
     </row>
     <row r="45" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="23">
         <v>8</v>
       </c>
       <c r="D45" s="3"/>
@@ -4369,7 +5841,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="30"/>
+      <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
@@ -4378,10 +5850,10 @@
       <c r="P45" s="3"/>
     </row>
     <row r="46" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="23">
         <v>4</v>
       </c>
       <c r="D46" s="3"/>
@@ -4390,7 +5862,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="30"/>
+      <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -4399,10 +5871,10 @@
       <c r="P46" s="3"/>
     </row>
     <row r="47" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="23">
         <v>6</v>
       </c>
       <c r="D47" s="3"/>
@@ -4411,7 +5883,7 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="30"/>
+      <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -4420,10 +5892,10 @@
       <c r="P47" s="3"/>
     </row>
     <row r="48" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="23">
         <v>4</v>
       </c>
       <c r="D48" s="3"/>
@@ -4432,7 +5904,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="30"/>
+      <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
@@ -4441,10 +5913,10 @@
       <c r="P48" s="3"/>
     </row>
     <row r="49" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="23">
         <v>8</v>
       </c>
       <c r="D49" s="3"/>
@@ -4453,7 +5925,7 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="30"/>
+      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
@@ -4462,10 +5934,10 @@
       <c r="P49" s="3"/>
     </row>
     <row r="50" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="23">
         <v>8</v>
       </c>
       <c r="D50" s="3"/>
@@ -4474,7 +5946,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="30"/>
+      <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -4483,10 +5955,10 @@
       <c r="P50" s="3"/>
     </row>
     <row r="51" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="35" t="s">
+      <c r="B51" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="23">
         <v>4</v>
       </c>
       <c r="D51" s="3"/>
@@ -4495,7 +5967,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="30"/>
+      <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -4504,10 +5976,10 @@
       <c r="P51" s="3"/>
     </row>
     <row r="52" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="23">
         <v>4</v>
       </c>
       <c r="D52" s="3"/>
@@ -4516,7 +5988,7 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="30"/>
+      <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -4525,10 +5997,10 @@
       <c r="P52" s="3"/>
     </row>
     <row r="53" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="23">
         <v>2</v>
       </c>
       <c r="D53" s="3"/>
@@ -4537,13 +6009,1139 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="30"/>
+      <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B99EEF-6F45-4A25-8EC4-EA62A83D2DB6}">
+  <dimension ref="B1:P53"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="23">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+    </row>
+    <row r="4" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="23">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="23">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="23">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+    </row>
+    <row r="7" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="23">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="23">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="23">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="23">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="23">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="23">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="23">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="23">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="23">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="23">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="23">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="23">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="23">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="23">
+        <v>4</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="23">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="23">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="23">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="23">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="23">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="23">
+        <v>4</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="23">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="23">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="23">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="23">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="36" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="23">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+    </row>
+    <row r="37" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="23">
+        <v>2</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+    </row>
+    <row r="38" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="23">
+        <v>4</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+    </row>
+    <row r="39" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="23"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="23"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" ht="26.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C43" s="23">
+        <v>8</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="23">
+        <v>6</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="23">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="33">
+        <v>4</v>
+      </c>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="34"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="34"/>
+      <c r="N46" s="34"/>
+      <c r="O46" s="34"/>
+      <c r="P46" s="34"/>
+    </row>
+    <row r="47" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="33">
+        <v>6</v>
+      </c>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="34"/>
+    </row>
+    <row r="48" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="33">
+        <v>4</v>
+      </c>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="34"/>
+      <c r="N48" s="34"/>
+      <c r="O48" s="34"/>
+      <c r="P48" s="34"/>
+    </row>
+    <row r="49" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="33">
+        <v>8</v>
+      </c>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="34"/>
+      <c r="N49" s="34"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="34"/>
+    </row>
+    <row r="50" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="33">
+        <v>8</v>
+      </c>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="34"/>
+      <c r="N50" s="34"/>
+      <c r="O50" s="34"/>
+      <c r="P50" s="34"/>
+    </row>
+    <row r="51" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="33">
+        <v>4</v>
+      </c>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="34"/>
+      <c r="N51" s="34"/>
+      <c r="O51" s="34"/>
+      <c r="P51" s="34"/>
+    </row>
+    <row r="52" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="33">
+        <v>4</v>
+      </c>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="34"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="34"/>
+      <c r="M52" s="34"/>
+      <c r="N52" s="34"/>
+      <c r="O52" s="34"/>
+      <c r="P52" s="34"/>
+    </row>
+    <row r="53" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="33">
+        <v>2</v>
+      </c>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="34"/>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/note/專案管理.xlsx
+++ b/note/專案管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aidara\note\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E046B63-1F95-4AB5-81A7-0726587BD86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7AF568-529F-4798-A88C-50A0E69A6D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="優照護模式比較" sheetId="2" r:id="rId1"/>
@@ -18,32 +18,22 @@
     <sheet name="WBS" sheetId="4" r:id="rId3"/>
     <sheet name="初階甘特圖" sheetId="5" r:id="rId4"/>
     <sheet name="初階甘特圖 (2)" sheetId="6" r:id="rId5"/>
+    <sheet name="工作表1" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">WBS!$A$1:$G$28</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="153">
   <si>
     <t>雇主</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -669,6 +659,22 @@
   </si>
   <si>
     <t>註冊/商店資訊模組v2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切換Boss頁面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>註冊Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇服務項目</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -904,6 +910,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -916,10 +926,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4042,14 +4048,14 @@
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="F7" s="30" t="s">
+      <c r="D7" s="31"/>
+      <c r="F7" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="33"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
@@ -4072,10 +4078,10 @@
       <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="29"/>
+      <c r="D9" s="31"/>
       <c r="F9" s="5" t="s">
         <v>31</v>
       </c>
@@ -4110,10 +4116,10 @@
       <c r="D11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
@@ -6979,169 +6985,169 @@
       <c r="B46" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="29">
         <v>4</v>
       </c>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="34"/>
-      <c r="N46" s="34"/>
-      <c r="O46" s="34"/>
-      <c r="P46" s="34"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
     </row>
     <row r="47" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="29">
         <v>6</v>
       </c>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
     </row>
     <row r="48" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="29">
         <v>4</v>
       </c>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="34"/>
-      <c r="N48" s="34"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
     </row>
     <row r="49" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="29">
         <v>8</v>
       </c>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="34"/>
-      <c r="N49" s="34"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
     </row>
     <row r="50" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="29">
         <v>8</v>
       </c>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
     </row>
     <row r="51" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="29">
         <v>4</v>
       </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="34"/>
-      <c r="N51" s="34"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
     </row>
     <row r="52" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C52" s="33">
+      <c r="C52" s="29">
         <v>4</v>
       </c>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="34"/>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
     </row>
     <row r="53" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="29">
         <v>2</v>
       </c>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="34"/>
-      <c r="M53" s="34"/>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7151,6 +7157,37 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B63F1F6-7438-4CFA-A62A-2A59DDB80011}">
+  <dimension ref="C3:E4"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{adaf7f72-99af-42e6-a6a5-1768b456778c}" enabled="1" method="Privileged" siteId="{bfaccad2-83f0-478b-a178-9e40a4734846}" contentBits="3" removed="0"/>

--- a/note/專案管理.xlsx
+++ b/note/專案管理.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aidara\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7AF568-529F-4798-A88C-50A0E69A6D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C55BA8F-DAF4-473F-A1D4-4A4A8ACF7DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="優照護模式比較" sheetId="2" r:id="rId1"/>
@@ -23,17 +23,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">WBS!$A$1:$G$28</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="218">
   <si>
     <t>雇主</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -675,6 +686,259 @@
   </si>
   <si>
     <t>選擇服務項目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/ServicesItem/categories</t>
+  </si>
+  <si>
+    <t>選擇價位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇服務方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output API URL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input API URL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/Location/cities</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇服務城市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/Location/districts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇服務行政區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>確認送出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/BossInfo/BossInfoQuestionSubmit</t>
+  </si>
+  <si>
+    <t>Boss頁面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>頭像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>評價</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成交次數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成交紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>評價紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帳號權限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前往設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服務項目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服務方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服務範圍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>價格區間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服務據點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>編輯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>認證檔案上傳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/BossInfo/upload-verification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前檔案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上傳檔案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/bossstorecontent/${userId}</t>
+  </si>
+  <si>
+    <t>個人化介紹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切換Customer頁面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇Google</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇FaceBook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選擇xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>google/auto</t>
+  </si>
+  <si>
+    <t>依分類查詢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/BossServices/stats/${itemId}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>店家清單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/BossServices/stores/${itemId}?cityId=${encodeURIComponent(cityId)}&amp;districtId=${encodeURIComponent(districtId)}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>單一店家詳細資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/BossServices/store/${userId}</t>
+  </si>
+  <si>
+    <t>/api/BossServices/categories</t>
+  </si>
+  <si>
+    <t>/api/CustomerServiceQuestionnaire/${USERID}</t>
+  </si>
+  <si>
+    <t>需求單城市分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服務店家城市分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求單行政區分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求單單一客戶資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>發起需求單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求單查詢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>認證狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>評分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一類評分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二類評分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三類評分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>留言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>總評分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>架構重寫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地區模組v2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -799,7 +1063,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -848,11 +1112,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -914,6 +1258,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3113,59 +3465,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>288270</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>94697</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>285749</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>226292</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="圖片 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73809CB9-264E-4A38-A242-430051A2ABF4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5727045" y="3733247"/>
-          <a:ext cx="607079" cy="131595"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>335140</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>87894</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>57857</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>219489</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3203,13 +3511,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>57970</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>110177</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>500591</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>241772</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3247,13 +3555,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>511882</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>91068</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>234600</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>222663</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3291,13 +3599,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>267559</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>107247</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>307975</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>238842</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3335,13 +3643,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>286609</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>94547</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>327025</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>226142</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3379,13 +3687,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>346782</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>110118</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>69500</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>241713</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3423,13 +3731,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>99132</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>116468</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>431450</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>248063</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3467,13 +3775,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>450270</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>103997</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>27262</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>235592</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3561,8 +3869,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>260902</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>321468</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3599,13 +3907,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>137821</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>214145</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3643,13 +3951,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>146050</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>588671</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>226845</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3675,6 +3983,182 @@
         <a:xfrm>
           <a:off x="6807200" y="4387850"/>
           <a:ext cx="442621" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>297626</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>90579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>396040</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>222174</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="圖片 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C734F1FF-E72C-41F2-96B2-4559C40D9B00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5746929" y="3750184"/>
+          <a:ext cx="1321624" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>363110</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>84626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>193411</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>216221</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="圖片 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E036AC6-1859-485A-B382-BC86180FEFF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7006798" y="4025595"/>
+          <a:ext cx="437519" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>214487</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>77647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>44788</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>209242</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="圖片 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC887F5E-9C94-4981-9064-619ACCEF6F8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7492901" y="4334337"/>
+          <a:ext cx="441215" cy="131595"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>327737</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>190695</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>312272</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="圖片 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C37F992-B93C-4890-99CD-D726802A9167}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5766512" y="3829245"/>
+          <a:ext cx="1967788" cy="121577"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4048,14 +4532,14 @@
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="F7" s="32" t="s">
+      <c r="D7" s="39"/>
+      <c r="F7" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
@@ -4078,10 +4562,10 @@
       <c r="B9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="39"/>
       <c r="F9" s="5" t="s">
         <v>31</v>
       </c>
@@ -4116,10 +4600,10 @@
       <c r="D11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="F11" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="42"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
@@ -6033,7 +6517,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B99EEF-6F45-4A25-8EC4-EA62A83D2DB6}">
-  <dimension ref="B1:P53"/>
+  <dimension ref="B1:P55"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -6918,12 +7402,12 @@
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="2:16" ht="26.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="26" t="s">
-        <v>148</v>
+    <row r="43" spans="2:16" ht="26.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="24" t="s">
+        <v>216</v>
       </c>
       <c r="C43" s="23">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -6941,10 +7425,10 @@
     </row>
     <row r="44" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="26" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="C44" s="23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -6961,11 +7445,11 @@
       <c r="P44" s="3"/>
     </row>
     <row r="45" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="28" t="s">
-        <v>97</v>
+      <c r="B45" s="25" t="s">
+        <v>217</v>
       </c>
       <c r="C45" s="23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -6982,50 +7466,50 @@
       <c r="P45" s="3"/>
     </row>
     <row r="46" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="29">
-        <v>4</v>
-      </c>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
+      <c r="C46" s="23">
+        <v>6</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
     </row>
     <row r="47" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="29">
+      <c r="B47" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="23">
         <v>6</v>
       </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
     </row>
     <row r="48" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="24" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C48" s="29">
         <v>4</v>
@@ -7046,10 +7530,10 @@
     </row>
     <row r="49" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D49" s="30"/>
       <c r="E49" s="30"/>
@@ -7067,10 +7551,10 @@
     </row>
     <row r="50" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="24" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C50" s="29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D50" s="30"/>
       <c r="E50" s="30"/>
@@ -7088,10 +7572,10 @@
     </row>
     <row r="51" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="24" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C51" s="29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D51" s="30"/>
       <c r="E51" s="30"/>
@@ -7109,10 +7593,10 @@
     </row>
     <row r="52" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="24" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C52" s="29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D52" s="30"/>
       <c r="E52" s="30"/>
@@ -7130,10 +7614,10 @@
     </row>
     <row r="53" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="24" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C53" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D53" s="30"/>
       <c r="E53" s="30"/>
@@ -7149,6 +7633,48 @@
       <c r="O53" s="30"/>
       <c r="P53" s="30"/>
     </row>
+    <row r="54" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="29">
+        <v>4</v>
+      </c>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+    </row>
+    <row r="55" spans="2:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="29">
+        <v>2</v>
+      </c>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7159,20 +7685,39 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B63F1F6-7438-4CFA-A62A-2A59DDB80011}">
-  <dimension ref="C3:E4"/>
+  <dimension ref="C2:M40"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="32.28515625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.28515625" customWidth="1"/>
+    <col min="10" max="11" width="115.5703125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="2" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C3" s="31" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="33"/>
+    </row>
+    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C4" s="34" t="s">
         <v>150</v>
       </c>
       <c r="D4" t="s">
@@ -7181,6 +7726,372 @@
       <c r="E4" t="s">
         <v>152</v>
       </c>
+      <c r="G4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C5" s="34"/>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="35"/>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C6" s="34"/>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C7" s="34"/>
+      <c r="E7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="35"/>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="34"/>
+      <c r="E8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8" s="35"/>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="34"/>
+      <c r="E9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I9" s="35"/>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="34"/>
+      <c r="D10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" t="s">
+        <v>166</v>
+      </c>
+      <c r="I10" s="35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="34"/>
+      <c r="F11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="34"/>
+      <c r="F12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" s="35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C13" s="34"/>
+      <c r="F13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C14" s="34"/>
+      <c r="F14" t="s">
+        <v>168</v>
+      </c>
+      <c r="I14" s="35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C15" s="34"/>
+      <c r="F15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I15" s="35" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C16" s="34"/>
+      <c r="F16" t="s">
+        <v>172</v>
+      </c>
+      <c r="I16" s="35"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C17" s="34"/>
+      <c r="E17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C18" s="34"/>
+      <c r="F18" t="s">
+        <v>178</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C19" s="34"/>
+      <c r="F19" t="s">
+        <v>179</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="34"/>
+      <c r="F20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C21" s="34"/>
+      <c r="E21" t="s">
+        <v>182</v>
+      </c>
+      <c r="F21" t="s">
+        <v>184</v>
+      </c>
+      <c r="I21" s="35"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C22" s="34"/>
+      <c r="F22" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" t="s">
+        <v>183</v>
+      </c>
+      <c r="I22" s="35"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C23" s="34"/>
+      <c r="F23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" s="35"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C24" s="34"/>
+      <c r="E24" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24" s="35"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C25" s="34"/>
+      <c r="D25" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" t="s">
+        <v>205</v>
+      </c>
+      <c r="I25" s="35" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C26" s="34"/>
+      <c r="D26" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" s="35"/>
+    </row>
+    <row r="27" spans="3:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="38"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C28" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C29" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" t="s">
+        <v>191</v>
+      </c>
+      <c r="H29" t="s">
+        <v>194</v>
+      </c>
+      <c r="I29" s="35"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C30" s="34"/>
+      <c r="E30" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" s="35"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="34"/>
+      <c r="E31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" s="35"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C32" s="34"/>
+      <c r="D32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" t="s">
+        <v>204</v>
+      </c>
+      <c r="F32" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="J32" t="s">
+        <v>198</v>
+      </c>
+      <c r="M32" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C33" s="34"/>
+      <c r="D33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" t="s">
+        <v>152</v>
+      </c>
+      <c r="G33" t="s">
+        <v>201</v>
+      </c>
+      <c r="I33" s="35"/>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C34" s="34"/>
+      <c r="E34" t="s">
+        <v>154</v>
+      </c>
+      <c r="I34" s="35"/>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C35" s="34"/>
+      <c r="E35" t="s">
+        <v>155</v>
+      </c>
+      <c r="I35" s="35"/>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C36" s="34"/>
+      <c r="E36" t="s">
+        <v>162</v>
+      </c>
+      <c r="H36" t="s">
+        <v>202</v>
+      </c>
+      <c r="I36" s="35"/>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C37" s="34"/>
+      <c r="D37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E37" t="s">
+        <v>211</v>
+      </c>
+      <c r="I37" s="35"/>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C38" s="34"/>
+      <c r="E38" t="s">
+        <v>212</v>
+      </c>
+      <c r="I38" s="35"/>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C39" s="34"/>
+      <c r="E39" t="s">
+        <v>213</v>
+      </c>
+      <c r="I39" s="35"/>
+    </row>
+    <row r="40" spans="3:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="36"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="38"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
